--- a/output/Data and Chart Outputs/india_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/india_hydro_reservoirs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Water year chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By reservoir" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Water year chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By reservoir" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -142,13 +142,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -170,8 +170,8 @@
             <v> </v>
           </tx>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -194,10 +194,10 @@
             <v>5-year range (2020/21-2024/25)</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="AFC6D9"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -227,7 +227,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="6E6E6E"/>
               </a:solidFill>
@@ -237,7 +237,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -263,7 +263,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+            <a:ln w="19050">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -273,7 +273,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -299,7 +299,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="0B3A66"/>
               </a:solidFill>
@@ -309,7 +309,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -340,8 +340,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -369,8 +369,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -389,7 +389,7 @@
         <majorUnit val="20"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -403,7 +403,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -427,9 +427,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1086,16 +1086,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77.53</v>
+        <v>69.91</v>
       </c>
       <c r="C11" t="n">
-        <v>8.09</v>
+        <v>15.71</v>
       </c>
       <c r="D11" t="n">
         <v>85.62</v>
       </c>
       <c r="E11" t="n">
-        <v>81.95999999999999</v>
+        <v>79.55</v>
       </c>
       <c r="F11" t="n">
         <v>85.62</v>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>77.69</v>
+        <v>67.86</v>
       </c>
       <c r="C12" t="n">
-        <v>7.36</v>
+        <v>17.19</v>
       </c>
       <c r="D12" t="n">
         <v>85.05</v>
       </c>
       <c r="E12" t="n">
-        <v>81.13</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>85.05</v>
@@ -1495,10 +1495,10 @@
         <v>83.27</v>
       </c>
       <c r="E27" t="n">
-        <v>74.98999999999999</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>70.77</v>
+        <v>82.98</v>
       </c>
       <c r="G27" t="n">
         <v>89.65000000000001</v>
@@ -1620,7 +1620,7 @@
         <v>83.75</v>
       </c>
       <c r="E32" t="n">
-        <v>75.33</v>
+        <v>76.86</v>
       </c>
       <c r="F32" t="n">
         <v>83.75</v>
@@ -1645,7 +1645,7 @@
         <v>84.45999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>75.44</v>
+        <v>76.67</v>
       </c>
       <c r="F33" t="n">
         <v>84.45999999999999</v>
@@ -1675,7 +1675,7 @@
         <v>84.39</v>
       </c>
       <c r="E34" t="n">
-        <v>75.16</v>
+        <v>76.08</v>
       </c>
       <c r="F34" t="n">
         <v>84.39</v>
@@ -1700,7 +1700,7 @@
         <v>81.63</v>
       </c>
       <c r="E35" t="n">
-        <v>74.59</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="F35" t="n">
         <v>81.63</v>
@@ -1725,7 +1725,7 @@
         <v>84.01000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>75.2</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="F36" t="n">
         <v>84.01000000000001</v>
@@ -1819,13 +1819,13 @@
         <v>60.85</v>
       </c>
       <c r="C40" t="n">
-        <v>21.95</v>
+        <v>22.7</v>
       </c>
       <c r="D40" t="n">
-        <v>82.8</v>
+        <v>83.55</v>
       </c>
       <c r="E40" t="n">
-        <v>75.93000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="F40" t="n">
         <v>82.8</v>
@@ -1844,13 +1844,13 @@
         <v>60.46</v>
       </c>
       <c r="C41" t="n">
-        <v>22.86</v>
+        <v>23.09</v>
       </c>
       <c r="D41" t="n">
-        <v>83.31999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="E41" t="n">
-        <v>74.41</v>
+        <v>77.27</v>
       </c>
       <c r="F41" t="n">
         <v>83.31999999999999</v>
@@ -1869,13 +1869,13 @@
         <v>60.42</v>
       </c>
       <c r="C42" t="n">
-        <v>22.56</v>
+        <v>23.13</v>
       </c>
       <c r="D42" t="n">
-        <v>82.98</v>
+        <v>83.55</v>
       </c>
       <c r="E42" t="n">
-        <v>74.84999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="F42" t="n">
         <v>82.98</v>
@@ -1994,13 +1994,13 @@
         <v>59.98</v>
       </c>
       <c r="C47" t="n">
-        <v>21.86</v>
+        <v>30.95</v>
       </c>
       <c r="D47" t="n">
-        <v>81.84</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>74.68000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="F47" t="n">
         <v>81.84</v>
@@ -2119,13 +2119,13 @@
         <v>59.74</v>
       </c>
       <c r="C52" t="n">
-        <v>21.68</v>
+        <v>23.75</v>
       </c>
       <c r="D52" t="n">
-        <v>81.42</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>74.05</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F52" t="n">
         <v>80.8</v>
@@ -2169,13 +2169,13 @@
         <v>59.12</v>
       </c>
       <c r="C54" t="n">
-        <v>24.43</v>
+        <v>22.38</v>
       </c>
       <c r="D54" t="n">
-        <v>83.55</v>
+        <v>81.5</v>
       </c>
       <c r="E54" t="n">
-        <v>76.91</v>
+        <v>75.89</v>
       </c>
       <c r="F54" t="n">
         <v>79.06999999999999</v>
@@ -2191,16 +2191,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>33.4</v>
+        <v>58.75</v>
       </c>
       <c r="C55" t="n">
-        <v>48.21</v>
+        <v>22.86</v>
       </c>
       <c r="D55" t="n">
         <v>81.61</v>
       </c>
       <c r="E55" t="n">
-        <v>70.59</v>
+        <v>75.66</v>
       </c>
       <c r="F55" t="n">
         <v>80.20999999999999</v>
@@ -2216,16 +2216,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52.31</v>
+        <v>58.39</v>
       </c>
       <c r="C56" t="n">
-        <v>27.96</v>
+        <v>21.88</v>
       </c>
       <c r="D56" t="n">
         <v>80.27</v>
       </c>
       <c r="E56" t="n">
-        <v>73.41</v>
+        <v>74.63</v>
       </c>
       <c r="F56" t="n">
         <v>77.02</v>
@@ -2899,19 +2899,19 @@
         <v>52.19</v>
       </c>
       <c r="C83" t="n">
-        <v>21.83</v>
+        <v>29.97</v>
       </c>
       <c r="D83" t="n">
-        <v>74.02</v>
+        <v>82.16</v>
       </c>
       <c r="E83" t="n">
-        <v>68.44</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F83" t="n">
         <v>72.93000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>91.68000000000001</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="84">
@@ -2924,19 +2924,19 @@
         <v>54.95</v>
       </c>
       <c r="C84" t="n">
-        <v>20.77</v>
+        <v>25.57</v>
       </c>
       <c r="D84" t="n">
-        <v>75.72</v>
+        <v>80.52</v>
       </c>
       <c r="E84" t="n">
-        <v>69.14</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F84" t="n">
         <v>72.12</v>
       </c>
       <c r="G84" t="n">
-        <v>78.56</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="85">
@@ -2949,19 +2949,19 @@
         <v>54.75</v>
       </c>
       <c r="C85" t="n">
-        <v>28.82</v>
+        <v>24.12</v>
       </c>
       <c r="D85" t="n">
-        <v>83.56999999999999</v>
+        <v>78.87</v>
       </c>
       <c r="E85" t="n">
-        <v>71.05</v>
+        <v>70.11</v>
       </c>
       <c r="F85" t="n">
         <v>73.01000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>91.63</v>
+        <v>85.86</v>
       </c>
     </row>
     <row r="86">
@@ -2974,13 +2974,13 @@
         <v>53.63</v>
       </c>
       <c r="C86" t="n">
-        <v>29.89</v>
+        <v>28.74</v>
       </c>
       <c r="D86" t="n">
-        <v>83.52</v>
+        <v>82.37</v>
       </c>
       <c r="E86" t="n">
-        <v>70.83</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="F86" t="n">
         <v>68.59</v>
@@ -2999,13 +2999,13 @@
         <v>54.65</v>
       </c>
       <c r="C87" t="n">
-        <v>35.32</v>
+        <v>28.19</v>
       </c>
       <c r="D87" t="n">
-        <v>89.97</v>
+        <v>82.84</v>
       </c>
       <c r="E87" t="n">
-        <v>71.40000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="F87" t="n">
         <v>71.48</v>
@@ -3024,13 +3024,13 @@
         <v>54.09</v>
       </c>
       <c r="C88" t="n">
-        <v>33.91</v>
+        <v>29.22</v>
       </c>
       <c r="D88" t="n">
-        <v>88</v>
+        <v>83.31</v>
       </c>
       <c r="E88" t="n">
-        <v>70.75</v>
+        <v>69.81</v>
       </c>
       <c r="F88" t="n">
         <v>71.06999999999999</v>
@@ -3099,13 +3099,13 @@
         <v>53.51</v>
       </c>
       <c r="C91" t="n">
-        <v>26.92</v>
+        <v>24.72</v>
       </c>
       <c r="D91" t="n">
-        <v>80.43000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="E91" t="n">
-        <v>69.36</v>
+        <v>68.92</v>
       </c>
       <c r="F91" t="n">
         <v>70.16</v>
@@ -3124,13 +3124,13 @@
         <v>53.22</v>
       </c>
       <c r="C92" t="n">
-        <v>28.39</v>
+        <v>24</v>
       </c>
       <c r="D92" t="n">
-        <v>81.61</v>
+        <v>77.22</v>
       </c>
       <c r="E92" t="n">
-        <v>68.42</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F92" t="n">
         <v>69.56999999999999</v>
@@ -3146,19 +3146,19 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>34.05</v>
+        <v>53.25</v>
       </c>
       <c r="C93" t="n">
-        <v>48.75</v>
+        <v>22.95</v>
       </c>
       <c r="D93" t="n">
-        <v>82.8</v>
+        <v>76.2</v>
       </c>
       <c r="E93" t="n">
-        <v>60.95</v>
+        <v>66.7</v>
       </c>
       <c r="F93" t="n">
-        <v>34.05</v>
+        <v>69.39</v>
       </c>
       <c r="G93" t="n">
         <v>73.88</v>
@@ -3210,7 +3210,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="E95" t="n">
-        <v>63.15</v>
+        <v>65.66</v>
       </c>
       <c r="F95" t="n">
         <v>68.88</v>
@@ -3229,16 +3229,16 @@
         <v>52.06</v>
       </c>
       <c r="C96" t="n">
-        <v>18.32</v>
+        <v>25.86</v>
       </c>
       <c r="D96" t="n">
-        <v>70.38</v>
+        <v>77.92</v>
       </c>
       <c r="E96" t="n">
-        <v>63.24</v>
+        <v>65.73</v>
       </c>
       <c r="F96" t="n">
-        <v>63.61</v>
+        <v>68.53</v>
       </c>
       <c r="G96" t="n">
         <v>72.95</v>
@@ -3254,13 +3254,13 @@
         <v>51.77</v>
       </c>
       <c r="C97" t="n">
-        <v>25.2</v>
+        <v>28.96</v>
       </c>
       <c r="D97" t="n">
-        <v>76.95999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="E97" t="n">
-        <v>65.77</v>
+        <v>66.52</v>
       </c>
       <c r="F97" t="n">
         <v>68.18000000000001</v>
@@ -3354,16 +3354,16 @@
         <v>50.89</v>
       </c>
       <c r="C101" t="n">
-        <v>33.13</v>
+        <v>32.69</v>
       </c>
       <c r="D101" t="n">
-        <v>84.02</v>
+        <v>83.58</v>
       </c>
       <c r="E101" t="n">
-        <v>68.73</v>
+        <v>67.16</v>
       </c>
       <c r="F101" t="n">
-        <v>84.02</v>
+        <v>76.14</v>
       </c>
       <c r="G101" t="n">
         <v>71.38</v>
@@ -3435,7 +3435,7 @@
         <v>80.05</v>
       </c>
       <c r="E104" t="n">
-        <v>63.45</v>
+        <v>65.11</v>
       </c>
       <c r="F104" t="n">
         <v>65.52</v>
@@ -3604,13 +3604,13 @@
         <v>48.78</v>
       </c>
       <c r="C111" t="n">
-        <v>18.57</v>
+        <v>24.11</v>
       </c>
       <c r="D111" t="n">
-        <v>67.34999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="E111" t="n">
-        <v>60.65</v>
+        <v>61.76</v>
       </c>
       <c r="F111" t="n">
         <v>62.54</v>
@@ -3629,13 +3629,13 @@
         <v>46.81</v>
       </c>
       <c r="C112" t="n">
-        <v>36.76</v>
+        <v>29.57</v>
       </c>
       <c r="D112" t="n">
-        <v>83.56999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="E112" t="n">
-        <v>63.16</v>
+        <v>61.73</v>
       </c>
       <c r="F112" t="n">
         <v>61.63</v>
@@ -3729,13 +3729,13 @@
         <v>47.43</v>
       </c>
       <c r="C116" t="n">
-        <v>24.95</v>
+        <v>34.16</v>
       </c>
       <c r="D116" t="n">
-        <v>72.38</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>61.09</v>
+        <v>62.93</v>
       </c>
       <c r="F116" t="n">
         <v>61.65</v>
@@ -3804,13 +3804,13 @@
         <v>46.62</v>
       </c>
       <c r="C119" t="n">
-        <v>34.38</v>
+        <v>31.76</v>
       </c>
       <c r="D119" t="n">
-        <v>81</v>
+        <v>78.38</v>
       </c>
       <c r="E119" t="n">
-        <v>61.78</v>
+        <v>61.25</v>
       </c>
       <c r="F119" t="n">
         <v>60.62</v>
@@ -3829,13 +3829,13 @@
         <v>45.94</v>
       </c>
       <c r="C120" t="n">
-        <v>33.93</v>
+        <v>28.68</v>
       </c>
       <c r="D120" t="n">
-        <v>79.87</v>
+        <v>74.62</v>
       </c>
       <c r="E120" t="n">
-        <v>61.55</v>
+        <v>60.5</v>
       </c>
       <c r="F120" t="n">
         <v>60.33</v>
@@ -3854,13 +3854,13 @@
         <v>46.11</v>
       </c>
       <c r="C121" t="n">
-        <v>21.97</v>
+        <v>24.75</v>
       </c>
       <c r="D121" t="n">
-        <v>68.08</v>
+        <v>70.86</v>
       </c>
       <c r="E121" t="n">
-        <v>58.97</v>
+        <v>59.53</v>
       </c>
       <c r="F121" t="n">
         <v>59.92</v>
@@ -3879,13 +3879,13 @@
         <v>48.68</v>
       </c>
       <c r="C122" t="n">
-        <v>13.3</v>
+        <v>18.42</v>
       </c>
       <c r="D122" t="n">
-        <v>61.98</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F122" t="n">
         <v>59.55</v>
@@ -3929,13 +3929,13 @@
         <v>44.51</v>
       </c>
       <c r="C124" t="n">
-        <v>30.66</v>
+        <v>20.52</v>
       </c>
       <c r="D124" t="n">
-        <v>75.17</v>
+        <v>65.03</v>
       </c>
       <c r="E124" t="n">
-        <v>59.37</v>
+        <v>57.34</v>
       </c>
       <c r="F124" t="n">
         <v>58.75</v>
@@ -3984,13 +3984,13 @@
         <v>51.58</v>
       </c>
       <c r="C126" t="n">
-        <v>14.67</v>
+        <v>19.34</v>
       </c>
       <c r="D126" t="n">
-        <v>66.25</v>
+        <v>70.92</v>
       </c>
       <c r="E126" t="n">
-        <v>58.39</v>
+        <v>59.32</v>
       </c>
       <c r="F126" t="n">
         <v>56.51</v>
@@ -4006,16 +4006,16 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>53.31</v>
+        <v>48.82</v>
       </c>
       <c r="C127" t="n">
-        <v>30.27</v>
+        <v>26.32</v>
       </c>
       <c r="D127" t="n">
-        <v>83.58</v>
+        <v>75.13</v>
       </c>
       <c r="E127" t="n">
-        <v>62.74</v>
+        <v>60.15</v>
       </c>
       <c r="F127" t="n">
         <v>57.63</v>
@@ -4034,13 +4034,13 @@
         <v>46.05</v>
       </c>
       <c r="C128" t="n">
-        <v>33.27</v>
+        <v>33.29</v>
       </c>
       <c r="D128" t="n">
-        <v>79.31999999999999</v>
+        <v>79.34</v>
       </c>
       <c r="E128" t="n">
-        <v>60.85</v>
+        <v>59.9</v>
       </c>
       <c r="F128" t="n">
         <v>57.1</v>
@@ -4084,13 +4084,13 @@
         <v>43.84</v>
       </c>
       <c r="C130" t="n">
-        <v>25.79</v>
+        <v>30.96</v>
       </c>
       <c r="D130" t="n">
-        <v>69.63</v>
+        <v>74.8</v>
       </c>
       <c r="E130" t="n">
-        <v>56.75</v>
+        <v>57.78</v>
       </c>
       <c r="F130" t="n">
         <v>56.39</v>
@@ -4134,13 +4134,13 @@
         <v>43.28</v>
       </c>
       <c r="C132" t="n">
-        <v>39.97</v>
+        <v>23.53</v>
       </c>
       <c r="D132" t="n">
-        <v>83.25</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="E132" t="n">
-        <v>59.16</v>
+        <v>55.87</v>
       </c>
       <c r="F132" t="n">
         <v>55.73</v>
@@ -4159,16 +4159,16 @@
         <v>43.03</v>
       </c>
       <c r="C133" t="n">
-        <v>29.19</v>
+        <v>24.55</v>
       </c>
       <c r="D133" t="n">
-        <v>72.22</v>
+        <v>67.58</v>
       </c>
       <c r="E133" t="n">
-        <v>58.67</v>
+        <v>55.71</v>
       </c>
       <c r="F133" t="n">
-        <v>65.48</v>
+        <v>55.32</v>
       </c>
       <c r="G133" t="n">
         <v>59.84</v>
@@ -4184,13 +4184,13 @@
         <v>42.45</v>
       </c>
       <c r="C134" t="n">
-        <v>18.74</v>
+        <v>25.89</v>
       </c>
       <c r="D134" t="n">
-        <v>61.19</v>
+        <v>68.34</v>
       </c>
       <c r="E134" t="n">
-        <v>54.16</v>
+        <v>55.59</v>
       </c>
       <c r="F134" t="n">
         <v>54.92</v>
@@ -4359,13 +4359,13 @@
         <v>40.99</v>
       </c>
       <c r="C141" t="n">
-        <v>42.56</v>
+        <v>23.97</v>
       </c>
       <c r="D141" t="n">
-        <v>83.55</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E141" t="n">
-        <v>56.75</v>
+        <v>53.03</v>
       </c>
       <c r="F141" t="n">
         <v>52.23</v>
@@ -4384,13 +4384,13 @@
         <v>40.71</v>
       </c>
       <c r="C142" t="n">
-        <v>42.84</v>
+        <v>24.46</v>
       </c>
       <c r="D142" t="n">
-        <v>83.55</v>
+        <v>65.17</v>
       </c>
       <c r="E142" t="n">
-        <v>57.42</v>
+        <v>53.75</v>
       </c>
       <c r="F142" t="n">
         <v>51.79</v>
@@ -4415,7 +4415,7 @@
         <v>65.39</v>
       </c>
       <c r="E143" t="n">
-        <v>54.45</v>
+        <v>53.49</v>
       </c>
       <c r="F143" t="n">
         <v>51.35</v>
@@ -4471,7 +4471,7 @@
         <v>52.92</v>
       </c>
       <c r="G145" t="n">
-        <v>63.51</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="146">
@@ -4764,13 +4764,13 @@
         <v>37.04</v>
       </c>
       <c r="C157" t="n">
-        <v>16.94</v>
+        <v>10.08</v>
       </c>
       <c r="D157" t="n">
-        <v>53.98</v>
+        <v>47.12</v>
       </c>
       <c r="E157" t="n">
-        <v>45.23</v>
+        <v>43.86</v>
       </c>
       <c r="F157" t="n">
         <v>46.08</v>
@@ -5211,16 +5211,16 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>20.03</v>
+        <v>32.71</v>
       </c>
       <c r="C175" t="n">
-        <v>22.98</v>
+        <v>10.3</v>
       </c>
       <c r="D175" t="n">
         <v>43.01</v>
       </c>
       <c r="E175" t="n">
-        <v>37.21</v>
+        <v>39.74</v>
       </c>
       <c r="F175" t="n">
         <v>42.17</v>
@@ -6274,13 +6274,13 @@
         <v>23.64</v>
       </c>
       <c r="C217" t="n">
-        <v>11.84</v>
+        <v>10.21</v>
       </c>
       <c r="D217" t="n">
-        <v>35.48</v>
+        <v>33.85</v>
       </c>
       <c r="E217" t="n">
-        <v>30.27</v>
+        <v>28.4</v>
       </c>
       <c r="F217" t="n">
         <v>26.53</v>
@@ -6330,7 +6330,7 @@
         <v>33.53</v>
       </c>
       <c r="E219" t="n">
-        <v>28.79</v>
+        <v>27.49</v>
       </c>
       <c r="F219" t="n">
         <v>26.13</v>
@@ -6405,7 +6405,7 @@
         <v>30.54</v>
       </c>
       <c r="E222" t="n">
-        <v>25.03</v>
+        <v>25.8</v>
       </c>
       <c r="F222" t="n">
         <v>25.23</v>
@@ -6424,13 +6424,13 @@
         <v>21.69</v>
       </c>
       <c r="C223" t="n">
-        <v>18.35</v>
+        <v>8.59</v>
       </c>
       <c r="D223" t="n">
-        <v>40.04</v>
+        <v>30.28</v>
       </c>
       <c r="E223" t="n">
-        <v>28.82</v>
+        <v>25.51</v>
       </c>
       <c r="F223" t="n">
         <v>27.29</v>
@@ -6449,13 +6449,13 @@
         <v>20.16</v>
       </c>
       <c r="C224" t="n">
-        <v>15.05</v>
+        <v>9.85</v>
       </c>
       <c r="D224" t="n">
-        <v>35.21</v>
+        <v>30.01</v>
       </c>
       <c r="E224" t="n">
-        <v>26.7</v>
+        <v>24.6</v>
       </c>
       <c r="F224" t="n">
         <v>24.67</v>
@@ -6499,13 +6499,13 @@
         <v>19.86</v>
       </c>
       <c r="C226" t="n">
-        <v>10.45</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D226" t="n">
-        <v>30.31</v>
+        <v>29.48</v>
       </c>
       <c r="E226" t="n">
-        <v>25.71</v>
+        <v>24.46</v>
       </c>
       <c r="F226" t="n">
         <v>24.24</v>
@@ -6986,7 +6986,7 @@
         <v>25.08</v>
       </c>
       <c r="G245" t="n">
-        <v>32.83</v>
+        <v>21.39</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -7204,13 +7204,13 @@
         <v>15.8</v>
       </c>
       <c r="C254" t="n">
-        <v>7.79</v>
+        <v>7.06</v>
       </c>
       <c r="D254" t="n">
-        <v>23.59</v>
+        <v>22.86</v>
       </c>
       <c r="E254" t="n">
-        <v>20.15</v>
+        <v>19.73</v>
       </c>
       <c r="F254" t="n">
         <v>21.79</v>
@@ -7229,13 +7229,13 @@
         <v>16.34</v>
       </c>
       <c r="C255" t="n">
-        <v>10.1</v>
+        <v>7.14</v>
       </c>
       <c r="D255" t="n">
-        <v>26.44</v>
+        <v>23.48</v>
       </c>
       <c r="E255" t="n">
-        <v>21.12</v>
+        <v>20.3</v>
       </c>
       <c r="F255" t="n">
         <v>23.48</v>
@@ -7585,7 +7585,7 @@
         <v>32.16</v>
       </c>
       <c r="E269" t="n">
-        <v>21.82</v>
+        <v>21.4</v>
       </c>
       <c r="F269" t="n">
         <v>32.16</v>
@@ -7610,7 +7610,7 @@
         <v>28.37</v>
       </c>
       <c r="E270" t="n">
-        <v>21.4</v>
+        <v>20.55</v>
       </c>
       <c r="F270" t="n">
         <v>28.37</v>
@@ -7626,16 +7626,16 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>6.76</v>
+        <v>15.28</v>
       </c>
       <c r="C271" t="n">
-        <v>27.8</v>
+        <v>19.28</v>
       </c>
       <c r="D271" t="n">
         <v>34.56</v>
       </c>
       <c r="E271" t="n">
-        <v>21.47</v>
+        <v>21.9</v>
       </c>
       <c r="F271" t="n">
         <v>34.56</v>
@@ -8156,16 +8156,16 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>29.39</v>
+        <v>27.85</v>
       </c>
       <c r="C292" t="n">
-        <v>25.4</v>
+        <v>26.94</v>
       </c>
       <c r="D292" t="n">
         <v>54.79</v>
       </c>
       <c r="E292" t="n">
-        <v>38.58</v>
+        <v>37.25</v>
       </c>
       <c r="F292" t="n">
         <v>54.79</v>
@@ -8240,7 +8240,7 @@
         <v>56.62</v>
       </c>
       <c r="E295" t="n">
-        <v>42.16</v>
+        <v>41.14</v>
       </c>
       <c r="F295" t="n">
         <v>56.62</v>
@@ -8281,16 +8281,16 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>30.8</v>
+        <v>33.83</v>
       </c>
       <c r="C297" t="n">
-        <v>27.23</v>
+        <v>24.2</v>
       </c>
       <c r="D297" t="n">
         <v>58.03</v>
       </c>
       <c r="E297" t="n">
-        <v>42.29</v>
+        <v>42.9</v>
       </c>
       <c r="F297" t="n">
         <v>58.03</v>
@@ -8381,16 +8381,16 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>13.12</v>
+        <v>43.16</v>
       </c>
       <c r="C301" t="n">
-        <v>50.79</v>
+        <v>20.75</v>
       </c>
       <c r="D301" t="n">
         <v>63.91</v>
       </c>
       <c r="E301" t="n">
-        <v>43.04</v>
+        <v>50.51</v>
       </c>
       <c r="F301" t="n">
         <v>63.91</v>
@@ -8409,16 +8409,16 @@
         <v>42.78</v>
       </c>
       <c r="C302" t="n">
-        <v>30.44</v>
+        <v>22.54</v>
       </c>
       <c r="D302" t="n">
-        <v>73.22</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="E302" t="n">
-        <v>53.52</v>
+        <v>51.95</v>
       </c>
       <c r="F302" t="n">
-        <v>73.22</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="G302" t="n">
         <v>36.63</v>
@@ -8440,7 +8440,7 @@
         <v>66.73999999999999</v>
       </c>
       <c r="E303" t="n">
-        <v>54.32</v>
+        <v>53.2</v>
       </c>
       <c r="F303" t="n">
         <v>66.73999999999999</v>
@@ -8490,7 +8490,7 @@
         <v>66.48</v>
       </c>
       <c r="E305" t="n">
-        <v>56.82</v>
+        <v>55.21</v>
       </c>
       <c r="F305" t="n">
         <v>66.48</v>
@@ -8506,16 +8506,16 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>18.3</v>
+        <v>47.8</v>
       </c>
       <c r="C306" t="n">
-        <v>51.44</v>
+        <v>21.94</v>
       </c>
       <c r="D306" t="n">
         <v>69.73999999999999</v>
       </c>
       <c r="E306" t="n">
-        <v>48.75</v>
+        <v>56.53</v>
       </c>
       <c r="F306" t="n">
         <v>69.73999999999999</v>
@@ -8545,7 +8545,7 @@
         <v>70.47</v>
       </c>
       <c r="E307" t="n">
-        <v>57.87</v>
+        <v>56.36</v>
       </c>
       <c r="F307" t="n">
         <v>70.47</v>
@@ -8701,7 +8701,7 @@
         <v>71.92</v>
       </c>
       <c r="G313" t="n">
-        <v>64.84999999999999</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="314">
@@ -8726,7 +8726,7 @@
         <v>72.06</v>
       </c>
       <c r="G314" t="n">
-        <v>52.66</v>
+        <v>57.39</v>
       </c>
     </row>
     <row r="315">
@@ -8751,7 +8751,7 @@
         <v>72.16</v>
       </c>
       <c r="G315" t="n">
-        <v>62.8</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="316">
@@ -8889,16 +8889,16 @@
         <v>56.25</v>
       </c>
       <c r="C321" t="n">
-        <v>27.8</v>
+        <v>18.34</v>
       </c>
       <c r="D321" t="n">
-        <v>84.05</v>
+        <v>74.59</v>
       </c>
       <c r="E321" t="n">
-        <v>70.92</v>
+        <v>68.41</v>
       </c>
       <c r="F321" t="n">
-        <v>84.05</v>
+        <v>74.59</v>
       </c>
       <c r="G321" t="n">
         <v>58.33</v>
@@ -8920,7 +8920,7 @@
         <v>75.65000000000001</v>
       </c>
       <c r="E322" t="n">
-        <v>68.78</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="F322" t="n">
         <v>75.65000000000001</v>
@@ -8945,7 +8945,7 @@
         <v>77.22</v>
       </c>
       <c r="E323" t="n">
-        <v>70.06</v>
+        <v>71.48</v>
       </c>
       <c r="F323" t="n">
         <v>77.22</v>
@@ -9020,7 +9020,7 @@
         <v>79.45</v>
       </c>
       <c r="E326" t="n">
-        <v>70.73999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="F326" t="n">
         <v>79.45</v>
@@ -9136,16 +9136,16 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>44.02</v>
+        <v>54.96</v>
       </c>
       <c r="C331" t="n">
-        <v>38.12</v>
+        <v>27.17</v>
       </c>
       <c r="D331" t="n">
         <v>82.14</v>
       </c>
       <c r="E331" t="n">
-        <v>69.39</v>
+        <v>71.58</v>
       </c>
       <c r="F331" t="n">
         <v>82.14</v>
@@ -9264,16 +9264,16 @@
         <v>54.62</v>
       </c>
       <c r="C336" t="n">
-        <v>26.15</v>
+        <v>30.55</v>
       </c>
       <c r="D336" t="n">
-        <v>80.77</v>
+        <v>85.17</v>
       </c>
       <c r="E336" t="n">
-        <v>73.02</v>
+        <v>74.98</v>
       </c>
       <c r="F336" t="n">
-        <v>75.34</v>
+        <v>85.17</v>
       </c>
       <c r="G336" t="n">
         <v>66.17</v>
@@ -9941,16 +9941,16 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>70.91</v>
+        <v>66.36</v>
       </c>
       <c r="C363" t="n">
-        <v>18.03</v>
+        <v>22.58</v>
       </c>
       <c r="D363" t="n">
         <v>88.94</v>
       </c>
       <c r="E363" t="n">
-        <v>81.23</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="F363" t="n">
         <v>88.94</v>
@@ -9966,16 +9966,16 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>74.8</v>
+        <v>65.69</v>
       </c>
       <c r="C364" t="n">
-        <v>14.14</v>
+        <v>23.25</v>
       </c>
       <c r="D364" t="n">
         <v>88.94</v>
       </c>
       <c r="E364" t="n">
-        <v>80.63</v>
+        <v>78.81</v>
       </c>
       <c r="F364" t="n">
         <v>88.94</v>
@@ -9991,16 +9991,16 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>75.23</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="C365" t="n">
-        <v>13.92</v>
+        <v>24.14</v>
       </c>
       <c r="D365" t="n">
         <v>89.15000000000001</v>
       </c>
       <c r="E365" t="n">
-        <v>80.62</v>
+        <v>79.14</v>
       </c>
       <c r="F365" t="n">
         <v>89.15000000000001</v>
@@ -10016,16 +10016,16 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>75.56</v>
+        <v>64.34</v>
       </c>
       <c r="C366" t="n">
-        <v>13.48</v>
+        <v>24.7</v>
       </c>
       <c r="D366" t="n">
         <v>89.04000000000001</v>
       </c>
       <c r="E366" t="n">
-        <v>82.93000000000001</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="F366" t="n">
         <v>89.04000000000001</v>
